--- a/data/Clinical_Data_Validation_Cohort.xlsx
+++ b/data/Clinical_Data_Validation_Cohort.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shawn\Box\NSCLC\Validation Cohort\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jasmin\大專生研究計畫\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F07F1B-3165-4BD8-9E42-BEB29CD8F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31DED50-6D9F-4BA0-9342-979FFD4394B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="15" windowWidth="12315" windowHeight="16282" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S1" sheetId="1" r:id="rId1"/>
@@ -390,104 +390,107 @@
     <t>Survival time (days)</t>
   </si>
   <si>
+    <t>Cigarette</t>
+  </si>
+  <si>
+    <t>Pack per year</t>
+  </si>
+  <si>
+    <t>Stage (TNM 8th edition)</t>
+  </si>
+  <si>
+    <t>EGFR</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>G12C</t>
+  </si>
+  <si>
+    <t>Exon 19</t>
+  </si>
+  <si>
+    <t>Exon 21</t>
+  </si>
+  <si>
+    <t>G12V</t>
+  </si>
+  <si>
+    <t>G12F</t>
+  </si>
+  <si>
+    <t>Exon 21 (L858R)</t>
+  </si>
+  <si>
+    <t>G12D</t>
+  </si>
+  <si>
+    <t>Exon 19 (24bp delete)</t>
+  </si>
+  <si>
+    <t>Exon 19 (9bp delete)</t>
+  </si>
+  <si>
+    <t>G12A</t>
+  </si>
+  <si>
+    <t>G13C</t>
+  </si>
+  <si>
+    <t>G13F</t>
+  </si>
+  <si>
+    <t>Exon 19 (15bp delete)</t>
+  </si>
+  <si>
+    <t>G13R</t>
+  </si>
+  <si>
+    <t>G12R</t>
+  </si>
+  <si>
+    <t>G13D</t>
+  </si>
+  <si>
+    <t>KRAS</t>
+  </si>
+  <si>
     <t>Event (death: 1, alive: 0)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>Tumor size (cm)</t>
-  </si>
-  <si>
-    <t>Cigarette</t>
-  </si>
-  <si>
-    <t>Pack per year</t>
-  </si>
-  <si>
-    <t>Stage (TNM 8th edition)</t>
-  </si>
-  <si>
-    <t>EGFR</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>G12C</t>
-  </si>
-  <si>
-    <t>Exon 19</t>
-  </si>
-  <si>
-    <t>Exon 21</t>
-  </si>
-  <si>
-    <t>G12V</t>
-  </si>
-  <si>
-    <t>G12F</t>
-  </si>
-  <si>
-    <t>Exon 21 (L858R)</t>
-  </si>
-  <si>
-    <t>G12D</t>
-  </si>
-  <si>
-    <t>Exon 19 (24bp delete)</t>
-  </si>
-  <si>
-    <t>Exon 19 (9bp delete)</t>
-  </si>
-  <si>
-    <t>G12A</t>
-  </si>
-  <si>
-    <t>G13C</t>
-  </si>
-  <si>
-    <t>G13F</t>
-  </si>
-  <si>
-    <t>Exon 19 (15bp delete)</t>
-  </si>
-  <si>
-    <t>G13R</t>
-  </si>
-  <si>
-    <t>G12R</t>
-  </si>
-  <si>
-    <t>G13D</t>
-  </si>
-  <si>
-    <t>KRAS</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>Grade</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -495,7 +498,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -503,7 +506,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -511,35 +514,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -547,7 +550,7 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -555,14 +558,14 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -570,14 +573,14 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -585,7 +588,7 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -593,14 +596,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -616,6 +619,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -993,48 +1003,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 輔色6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 輔色6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="輔色3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="輔色4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="輔色5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="輔色6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="標題" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="標題 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="標題 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="標題 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="標題 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="輸入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="輸出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="檢查儲存格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1050,9 +1060,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1090,7 +1100,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1196,7 +1206,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1338,7 +1348,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1347,10 +1357,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N96"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.46484375" customWidth="1"/>
+    <col min="2" max="2" width="18.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -1358,14 +1368,14 @@
     <col min="7" max="7" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>118</v>
       </c>
@@ -1373,16 +1383,16 @@
         <v>119</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>144</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>0</v>
@@ -1391,25 +1401,25 @@
         <v>1</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="N1" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1535,13 +1545,13 @@
         <v>1</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1579,13 +1589,13 @@
         <v>1</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -1623,13 +1633,13 @@
         <v>1</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1667,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1711,13 +1721,13 @@
         <v>2</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1755,13 +1765,13 @@
         <v>2</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1799,13 +1809,13 @@
         <v>2</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,13 +1853,13 @@
         <v>1</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1887,13 +1897,13 @@
         <v>1</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -1931,13 +1941,13 @@
         <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -1975,13 +1985,13 @@
         <v>2</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -2019,13 +2029,13 @@
         <v>1</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -2063,13 +2073,13 @@
         <v>2</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -2107,13 +2117,13 @@
         <v>1</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -2151,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2195,13 +2205,13 @@
         <v>2</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,13 +2249,13 @@
         <v>2</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -2283,13 +2293,13 @@
         <v>2</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -2327,13 +2337,13 @@
         <v>2</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>41</v>
       </c>
@@ -2371,13 +2381,13 @@
         <v>2</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -2415,13 +2425,13 @@
         <v>2</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
@@ -2459,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>44</v>
       </c>
@@ -2503,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>45</v>
       </c>
@@ -2547,13 +2557,13 @@
         <v>2</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>46</v>
       </c>
@@ -2591,13 +2601,13 @@
         <v>1</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>47</v>
       </c>
@@ -2635,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>48</v>
       </c>
@@ -2679,13 +2689,13 @@
         <v>1</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>49</v>
       </c>
@@ -2723,13 +2733,13 @@
         <v>1</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>50</v>
       </c>
@@ -2767,13 +2777,13 @@
         <v>2</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>51</v>
       </c>
@@ -2811,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>53</v>
       </c>
@@ -2855,13 +2865,13 @@
         <v>1</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>54</v>
       </c>
@@ -2899,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
@@ -2943,13 +2953,13 @@
         <v>1</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>56</v>
       </c>
@@ -2987,13 +2997,13 @@
         <v>3</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>57</v>
       </c>
@@ -3031,13 +3041,13 @@
         <v>3</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>58</v>
       </c>
@@ -3075,13 +3085,13 @@
         <v>3</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,7 +3135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>60</v>
       </c>
@@ -3163,13 +3173,13 @@
         <v>3</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>61</v>
       </c>
@@ -3207,13 +3217,13 @@
         <v>3</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>62</v>
       </c>
@@ -3251,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>63</v>
       </c>
@@ -3295,13 +3305,13 @@
         <v>3</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>64</v>
       </c>
@@ -3339,13 +3349,13 @@
         <v>3</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
@@ -3383,13 +3393,13 @@
         <v>3</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>66</v>
       </c>
@@ -3427,13 +3437,13 @@
         <v>3</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>67</v>
       </c>
@@ -3471,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>68</v>
       </c>
@@ -3515,13 +3525,13 @@
         <v>3</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>69</v>
       </c>
@@ -3559,13 +3569,13 @@
         <v>3</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>70</v>
       </c>
@@ -3603,13 +3613,13 @@
         <v>3</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>71</v>
       </c>
@@ -3647,13 +3657,13 @@
         <v>3</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>72</v>
       </c>
@@ -3691,13 +3701,13 @@
         <v>3</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>73</v>
       </c>
@@ -3735,13 +3745,13 @@
         <v>3</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>74</v>
       </c>
@@ -3779,13 +3789,13 @@
         <v>3</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>76</v>
       </c>
@@ -3823,13 +3833,13 @@
         <v>3</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>77</v>
       </c>
@@ -3867,13 +3877,13 @@
         <v>3</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>78</v>
       </c>
@@ -3911,13 +3921,13 @@
         <v>3</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
@@ -3961,7 +3971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>80</v>
       </c>
@@ -3999,13 +4009,13 @@
         <v>3</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
@@ -4043,13 +4053,13 @@
         <v>3</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>82</v>
       </c>
@@ -4087,13 +4097,13 @@
         <v>3</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>83</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>84</v>
       </c>
@@ -4175,13 +4185,13 @@
         <v>3</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>85</v>
       </c>
@@ -4225,7 +4235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>86</v>
       </c>
@@ -4263,13 +4273,13 @@
         <v>3</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>88</v>
       </c>
@@ -4307,13 +4317,13 @@
         <v>3</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>89</v>
       </c>
@@ -4357,7 +4367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>90</v>
       </c>
@@ -4395,13 +4405,13 @@
         <v>3</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>91</v>
       </c>
@@ -4439,13 +4449,13 @@
         <v>3</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>92</v>
       </c>
@@ -4483,13 +4493,13 @@
         <v>3</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>93</v>
       </c>
@@ -4527,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>94</v>
       </c>
@@ -4571,13 +4581,13 @@
         <v>3</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
         <v>95</v>
       </c>
@@ -4615,13 +4625,13 @@
         <v>3</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
         <v>96</v>
       </c>
@@ -4665,7 +4675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>97</v>
       </c>
@@ -4703,13 +4713,13 @@
         <v>3</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>98</v>
       </c>
@@ -4753,7 +4763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>99</v>
       </c>
@@ -4791,13 +4801,13 @@
         <v>3</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>100</v>
       </c>
@@ -4835,13 +4845,13 @@
         <v>3</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
         <v>101</v>
       </c>
@@ -4879,13 +4889,13 @@
         <v>3</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
         <v>102</v>
       </c>
@@ -4929,7 +4939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>103</v>
       </c>
@@ -4967,13 +4977,13 @@
         <v>3</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>104</v>
       </c>
@@ -5011,13 +5021,13 @@
         <v>3</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>105</v>
       </c>
@@ -5055,13 +5065,13 @@
         <v>3</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>106</v>
       </c>
@@ -5099,13 +5109,13 @@
         <v>3</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N85" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>107</v>
       </c>
@@ -5143,13 +5153,13 @@
         <v>3</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>108</v>
       </c>
@@ -5187,13 +5197,13 @@
         <v>3</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>109</v>
       </c>
@@ -5231,13 +5241,13 @@
         <v>3</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>110</v>
       </c>
@@ -5275,13 +5285,13 @@
         <v>3</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>111</v>
       </c>
@@ -5319,13 +5329,13 @@
         <v>3</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>112</v>
       </c>
@@ -5363,13 +5373,13 @@
         <v>3</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>113</v>
       </c>
@@ -5407,13 +5417,13 @@
         <v>3</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>114</v>
       </c>
@@ -5451,13 +5461,13 @@
         <v>3</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>115</v>
       </c>
@@ -5495,13 +5505,13 @@
         <v>3</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>116</v>
       </c>
@@ -5539,13 +5549,13 @@
         <v>3</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>117</v>
       </c>
@@ -5583,13 +5593,14 @@
         <v>3</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>